--- a/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_2048_run3/epoch_120/per_file_predictions_epoch_120.xlsx
+++ b/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_2048_run3/epoch_120/per_file_predictions_epoch_120.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="518">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="521">
   <si>
     <t>Filename</t>
   </si>
@@ -808,766 +808,775 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0.9751,0.0076,0.0037,0.0056</t>
-  </si>
-  <si>
-    <t>0.0140,0.0002,0.0001,0.9964</t>
-  </si>
-  <si>
-    <t>0.9734,0.0031,0.0009,0.0131</t>
-  </si>
-  <si>
-    <t>0.0946,0.0023,0.0016,0.9683</t>
-  </si>
-  <si>
-    <t>0.9984,0.0011,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9969,0.0014,0.0005,0.0002</t>
-  </si>
-  <si>
-    <t>0.9984,0.0009,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9990,0.0003,0.0000,0.0002</t>
-  </si>
-  <si>
-    <t>0.9941,0.0038,0.0010,0.0004</t>
-  </si>
-  <si>
-    <t>0.9972,0.0016,0.0003,0.0002</t>
-  </si>
-  <si>
-    <t>0.9966,0.0010,0.0005,0.0006</t>
-  </si>
-  <si>
-    <t>0.9984,0.0007,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.9429,0.0023,0.0803,0.0004</t>
-  </si>
-  <si>
-    <t>0.8857,0.0303,0.0708,0.0033</t>
-  </si>
-  <si>
-    <t>0.6709,0.0128,0.4056,0.0019</t>
-  </si>
-  <si>
-    <t>0.0954,0.0234,0.8726,0.0169</t>
-  </si>
-  <si>
-    <t>0.9829,0.0030,0.0063,0.0008</t>
-  </si>
-  <si>
-    <t>0.0039,0.9925,0.0029,0.0003</t>
-  </si>
-  <si>
-    <t>0.0093,0.9819,0.0053,0.0015</t>
-  </si>
-  <si>
-    <t>0.0547,0.9213,0.0369,0.0050</t>
-  </si>
-  <si>
-    <t>0.0192,0.9820,0.0049,0.0001</t>
-  </si>
-  <si>
-    <t>0.0005,0.9989,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.9459,0.0031,0.0339,0.0038</t>
-  </si>
-  <si>
-    <t>0.3704,0.0013,0.7848,0.0012</t>
-  </si>
-  <si>
-    <t>0.0695,0.0005,0.9707,0.0001</t>
-  </si>
-  <si>
-    <t>0.3179,0.0412,0.6524,0.0067</t>
-  </si>
-  <si>
-    <t>0.0168,0.0026,0.9838,0.0020</t>
-  </si>
-  <si>
-    <t>0.0477,0.0022,0.9644,0.0054</t>
-  </si>
-  <si>
-    <t>0.0092,0.0004,0.9960,0.0002</t>
-  </si>
-  <si>
-    <t>0.7169,0.3575,0.0114,0.0017</t>
-  </si>
-  <si>
-    <t>0.6764,0.1910,0.1470,0.0062</t>
-  </si>
-  <si>
-    <t>0.0009,0.0077,0.9989,0.0002</t>
-  </si>
-  <si>
-    <t>0.0184,0.9378,0.0472,0.0005</t>
-  </si>
-  <si>
-    <t>0.9622,0.0214,0.0083,0.0030</t>
-  </si>
-  <si>
-    <t>0.9095,0.0310,0.0554,0.0024</t>
-  </si>
-  <si>
-    <t>0.8863,0.2796,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.0080,0.9809,0.0191,0.0025</t>
-  </si>
-  <si>
-    <t>0.0425,0.7138,0.1098,0.0200</t>
-  </si>
-  <si>
-    <t>0.0344,0.0036,0.9505,0.0057</t>
-  </si>
-  <si>
-    <t>0.3760,0.0049,0.7812,0.0016</t>
-  </si>
-  <si>
-    <t>0.0707,0.0105,0.9359,0.0091</t>
-  </si>
-  <si>
-    <t>0.0304,0.0983,0.9762,0.0006</t>
-  </si>
-  <si>
-    <t>0.0019,0.9936,0.0006,0.0002</t>
-  </si>
-  <si>
-    <t>0.0009,0.0073,0.9966,0.0023</t>
-  </si>
-  <si>
-    <t>0.0383,0.8196,0.0389,0.4682</t>
-  </si>
-  <si>
-    <t>0.0028,0.9807,0.0819,0.0417</t>
-  </si>
-  <si>
-    <t>0.0738,0.9222,0.0174,0.0005</t>
-  </si>
-  <si>
-    <t>0.0027,0.9929,0.0617,0.0004</t>
-  </si>
-  <si>
-    <t>0.0009,0.0140,0.9930,0.0028</t>
-  </si>
-  <si>
-    <t>0.0029,0.0612,0.9941,0.0001</t>
-  </si>
-  <si>
-    <t>0.0401,0.0020,0.9620,0.0070</t>
-  </si>
-  <si>
-    <t>0.0062,0.0017,0.9955,0.0005</t>
-  </si>
-  <si>
-    <t>0.0031,0.0046,0.9956,0.0003</t>
-  </si>
-  <si>
-    <t>0.0020,0.0528,0.9916,0.0003</t>
-  </si>
-  <si>
-    <t>0.9672,0.0475,0.0038,0.0006</t>
-  </si>
-  <si>
-    <t>0.9695,0.0070,0.0212,0.0008</t>
-  </si>
-  <si>
-    <t>0.9913,0.0007,0.0066,0.0002</t>
-  </si>
-  <si>
-    <t>0.0019,0.0907,0.9920,0.0315</t>
-  </si>
-  <si>
-    <t>0.9943,0.0043,0.0008,0.0004</t>
-  </si>
-  <si>
-    <t>0.9991,0.0003,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9945,0.0037,0.0009,0.0003</t>
-  </si>
-  <si>
-    <t>0.0006,0.9461,0.9898,0.0001</t>
-  </si>
-  <si>
-    <t>0.0023,0.0389,0.9953,0.0005</t>
-  </si>
-  <si>
-    <t>0.0110,0.0029,0.9864,0.0010</t>
-  </si>
-  <si>
-    <t>0.0003,0.9429,0.9947,0.0000</t>
-  </si>
-  <si>
-    <t>0.0009,0.0015,0.9985,0.0003</t>
-  </si>
-  <si>
-    <t>0.0233,0.9745,0.0019,0.0000</t>
-  </si>
-  <si>
-    <t>0.0022,0.9970,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.3325,0.0075,0.7835,0.0060</t>
-  </si>
-  <si>
-    <t>0.7138,0.0668,0.2569,0.0023</t>
-  </si>
-  <si>
-    <t>0.0134,0.0286,0.9850,0.0082</t>
-  </si>
-  <si>
-    <t>0.0034,0.9649,0.5883,0.0004</t>
-  </si>
-  <si>
-    <t>0.0085,0.7959,0.7579,0.0011</t>
-  </si>
-  <si>
-    <t>0.0010,0.9949,0.0326,0.0004</t>
-  </si>
-  <si>
-    <t>0.0006,0.9845,0.9077,0.0001</t>
-  </si>
-  <si>
-    <t>0.0311,0.0007,0.0019,0.9873</t>
-  </si>
-  <si>
-    <t>0.0023,0.0014,0.0000,0.9989</t>
-  </si>
-  <si>
-    <t>0.0334,0.0002,0.0003,0.9917</t>
-  </si>
-  <si>
-    <t>0.0140,0.0011,0.0009,0.9938</t>
-  </si>
-  <si>
-    <t>0.0378,0.0026,0.0050,0.9767</t>
-  </si>
-  <si>
-    <t>0.0032,0.0323,0.0004,0.9947</t>
-  </si>
-  <si>
-    <t>0.0006,0.9609,0.9664,0.0001</t>
-  </si>
-  <si>
-    <t>0.0021,0.8850,0.9796,0.0002</t>
-  </si>
-  <si>
-    <t>0.0095,0.4928,0.8248,0.0031</t>
-  </si>
-  <si>
-    <t>0.0070,0.2282,0.9762,0.0004</t>
-  </si>
-  <si>
-    <t>0.0026,0.9840,0.3016,0.0002</t>
-  </si>
-  <si>
-    <t>0.0012,0.9810,0.4490,0.0003</t>
-  </si>
-  <si>
-    <t>0.9957,0.0017,0.0009,0.0004</t>
-  </si>
-  <si>
-    <t>0.9966,0.0018,0.0005,0.0002</t>
-  </si>
-  <si>
-    <t>0.9951,0.0033,0.0006,0.0003</t>
-  </si>
-  <si>
-    <t>0.9970,0.0009,0.0003,0.0007</t>
-  </si>
-  <si>
-    <t>0.9971,0.0015,0.0003,0.0003</t>
-  </si>
-  <si>
-    <t>0.9966,0.0018,0.0004,0.0004</t>
-  </si>
-  <si>
-    <t>0.9981,0.0008,0.0002,0.0002</t>
-  </si>
-  <si>
-    <t>0.9831,0.0184,0.0018,0.0006</t>
-  </si>
-  <si>
-    <t>0.9991,0.0002,0.0000,0.0002</t>
-  </si>
-  <si>
-    <t>0.9990,0.0004,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9992,0.0001,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9993,0.0001,0.0000,0.0002</t>
-  </si>
-  <si>
-    <t>0.9987,0.0006,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9990,0.0003,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.9983,0.0004,0.0002,0.0004</t>
-  </si>
-  <si>
-    <t>0.9978,0.0003,0.0001,0.0008</t>
-  </si>
-  <si>
-    <t>0.0018,0.0012,0.9964,0.0042</t>
-  </si>
-  <si>
-    <t>0.0971,0.0221,0.9421,0.0004</t>
-  </si>
-  <si>
-    <t>0.9355,0.0027,0.0337,0.0059</t>
-  </si>
-  <si>
-    <t>0.0018,0.0014,0.9978,0.0002</t>
-  </si>
-  <si>
-    <t>0.0055,0.9907,0.0010,0.0005</t>
-  </si>
-  <si>
-    <t>0.0096,0.9870,0.0028,0.0003</t>
-  </si>
-  <si>
-    <t>0.2969,0.8189,0.0016,0.0002</t>
-  </si>
-  <si>
-    <t>0.0087,0.9884,0.0027,0.0002</t>
-  </si>
-  <si>
-    <t>0.0143,0.9859,0.0032,0.0001</t>
-  </si>
-  <si>
-    <t>0.0009,0.9981,0.0004,0.0001</t>
-  </si>
-  <si>
-    <t>0.6785,0.4805,0.0031,0.0001</t>
-  </si>
-  <si>
-    <t>0.7634,0.0561,0.1834,0.0369</t>
-  </si>
-  <si>
-    <t>0.6876,0.0030,0.5043,0.0005</t>
-  </si>
-  <si>
-    <t>0.3460,0.0074,0.7066,0.0106</t>
-  </si>
-  <si>
-    <t>0.4936,0.0175,0.5816,0.0018</t>
-  </si>
-  <si>
-    <t>0.0658,0.0320,0.0893,0.9281</t>
-  </si>
-  <si>
-    <t>0.0089,0.9851,0.0147,0.0009</t>
-  </si>
-  <si>
-    <t>0.0033,0.9884,0.0247,0.0021</t>
-  </si>
-  <si>
-    <t>0.0016,0.9963,0.0016,0.0002</t>
-  </si>
-  <si>
-    <t>0.0067,0.9818,0.0605,0.0029</t>
-  </si>
-  <si>
-    <t>0.0398,0.9646,0.0022,0.0005</t>
-  </si>
-  <si>
-    <t>0.6074,0.4588,0.0187,0.0015</t>
-  </si>
-  <si>
-    <t>0.8101,0.2045,0.0140,0.0005</t>
-  </si>
-  <si>
-    <t>0.9984,0.0002,0.0004,0.0001</t>
-  </si>
-  <si>
-    <t>0.9964,0.0008,0.0011,0.0002</t>
-  </si>
-  <si>
-    <t>0.9974,0.0004,0.0002,0.0007</t>
-  </si>
-  <si>
-    <t>0.9986,0.0004,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.9968,0.0003,0.0004,0.0009</t>
-  </si>
-  <si>
-    <t>0.9983,0.0002,0.0004,0.0001</t>
-  </si>
-  <si>
-    <t>0.9986,0.0003,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.9985,0.0008,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.0015,0.2793,0.9915,0.0005</t>
-  </si>
-  <si>
-    <t>0.0006,0.1909,0.9959,0.0001</t>
-  </si>
-  <si>
-    <t>0.0027,0.0179,0.9891,0.0007</t>
-  </si>
-  <si>
-    <t>0.0089,0.0298,0.9708,0.0008</t>
-  </si>
-  <si>
-    <t>0.9539,0.0108,0.0159,0.0033</t>
-  </si>
-  <si>
-    <t>0.9699,0.0024,0.0167,0.0010</t>
-  </si>
-  <si>
-    <t>0.4848,0.0008,0.7904,0.0002</t>
-  </si>
-  <si>
-    <t>0.9791,0.0005,0.0259,0.0001</t>
-  </si>
-  <si>
-    <t>0.1691,0.0008,0.0008,0.9562</t>
-  </si>
-  <si>
-    <t>0.0002,0.0007,0.0001,0.9997</t>
-  </si>
-  <si>
-    <t>0.0029,0.0051,0.0008,0.9974</t>
-  </si>
-  <si>
-    <t>0.0046,0.0003,0.0002,0.9981</t>
-  </si>
-  <si>
-    <t>0.0023,0.7287,0.9805,0.0005</t>
-  </si>
-  <si>
-    <t>0.9938,0.0008,0.0003,0.0033</t>
-  </si>
-  <si>
-    <t>0.0628,0.9464,0.0052,0.0025</t>
-  </si>
-  <si>
-    <t>0.9903,0.0030,0.0021,0.0017</t>
-  </si>
-  <si>
-    <t>0.6596,0.4284,0.0088,0.0030</t>
-  </si>
-  <si>
-    <t>0.9887,0.0022,0.0045,0.0009</t>
-  </si>
-  <si>
-    <t>0.6672,0.0515,0.0384,0.3766</t>
-  </si>
-  <si>
-    <t>0.9944,0.0026,0.0009,0.0006</t>
-  </si>
-  <si>
-    <t>0.0051,0.7039,0.9425,0.0097</t>
-  </si>
-  <si>
-    <t>0.9912,0.0001,0.0006,0.0046</t>
-  </si>
-  <si>
-    <t>0.9877,0.0024,0.0025,0.0028</t>
-  </si>
-  <si>
-    <t>0.2404,0.8050,0.0142,0.0023</t>
-  </si>
-  <si>
-    <t>0.9933,0.0018,0.0014,0.0002</t>
-  </si>
-  <si>
-    <t>0.9412,0.0542,0.0067,0.0012</t>
-  </si>
-  <si>
-    <t>0.1678,0.1473,0.6349,0.0060</t>
-  </si>
-  <si>
-    <t>0.8681,0.0256,0.1202,0.0032</t>
-  </si>
-  <si>
-    <t>0.9407,0.0495,0.0089,0.0015</t>
-  </si>
-  <si>
-    <t>0.9901,0.0062,0.0015,0.0013</t>
-  </si>
-  <si>
-    <t>0.9968,0.0019,0.0003,0.0004</t>
-  </si>
-  <si>
-    <t>0.9957,0.0034,0.0004,0.0002</t>
-  </si>
-  <si>
-    <t>0.9972,0.0007,0.0007,0.0002</t>
-  </si>
-  <si>
-    <t>0.9930,0.0013,0.0013,0.0012</t>
-  </si>
-  <si>
-    <t>0.9956,0.0025,0.0006,0.0002</t>
-  </si>
-  <si>
-    <t>0.9945,0.0012,0.0022,0.0004</t>
-  </si>
-  <si>
-    <t>0.9958,0.0015,0.0003,0.0006</t>
-  </si>
-  <si>
-    <t>0.9866,0.0106,0.0004,0.0008</t>
-  </si>
-  <si>
-    <t>0.8885,0.1301,0.0072,0.0003</t>
-  </si>
-  <si>
-    <t>0.3777,0.7031,0.0074,0.0013</t>
-  </si>
-  <si>
-    <t>0.0047,0.0763,0.9921,0.0026</t>
-  </si>
-  <si>
-    <t>0.9897,0.0065,0.0017,0.0007</t>
-  </si>
-  <si>
-    <t>0.9939,0.0044,0.0008,0.0004</t>
-  </si>
-  <si>
-    <t>0.9851,0.0061,0.0073,0.0008</t>
-  </si>
-  <si>
-    <t>0.9860,0.0078,0.0029,0.0012</t>
-  </si>
-  <si>
-    <t>0.0026,0.0114,0.9969,0.0005</t>
-  </si>
-  <si>
-    <t>0.9927,0.0031,0.0009,0.0010</t>
-  </si>
-  <si>
-    <t>0.0065,0.0032,0.9913,0.0009</t>
-  </si>
-  <si>
-    <t>0.0025,0.0519,0.9919,0.0024</t>
-  </si>
-  <si>
-    <t>0.0059,0.0015,0.9937,0.0014</t>
-  </si>
-  <si>
-    <t>0.0046,0.0065,0.9933,0.0011</t>
-  </si>
-  <si>
-    <t>0.0033,0.0095,0.9914,0.0017</t>
-  </si>
-  <si>
-    <t>0.0526,0.0002,0.9791,0.0001</t>
-  </si>
-  <si>
-    <t>0.0053,0.0026,0.9945,0.0008</t>
-  </si>
-  <si>
-    <t>0.2474,0.0147,0.8281,0.0035</t>
-  </si>
-  <si>
-    <t>0.0903,0.0035,0.9340,0.0020</t>
-  </si>
-  <si>
-    <t>0.3065,0.0208,0.7227,0.0064</t>
-  </si>
-  <si>
-    <t>0.0307,0.7256,0.3334,0.0044</t>
-  </si>
-  <si>
-    <t>0.0980,0.1215,0.7847,0.0059</t>
-  </si>
-  <si>
-    <t>0.9485,0.0002,0.1142,0.0000</t>
-  </si>
-  <si>
-    <t>0.9308,0.0049,0.0550,0.0022</t>
-  </si>
-  <si>
-    <t>0.1163,0.0227,0.9020,0.0019</t>
-  </si>
-  <si>
-    <t>0.0374,0.9659,0.0007,0.0009</t>
-  </si>
-  <si>
-    <t>0.1356,0.9079,0.0013,0.0005</t>
-  </si>
-  <si>
-    <t>0.9779,0.0384,0.0011,0.0003</t>
-  </si>
-  <si>
-    <t>0.9853,0.0141,0.0025,0.0010</t>
-  </si>
-  <si>
-    <t>0.0026,0.9949,0.0009,0.0025</t>
-  </si>
-  <si>
-    <t>0.9771,0.0094,0.0054,0.0003</t>
-  </si>
-  <si>
-    <t>0.9730,0.0008,0.0201,0.0008</t>
-  </si>
-  <si>
-    <t>0.9521,0.0014,0.0375,0.0012</t>
-  </si>
-  <si>
-    <t>0.7046,0.0150,0.3690,0.0073</t>
-  </si>
-  <si>
-    <t>0.7270,0.0016,0.3430,0.0042</t>
-  </si>
-  <si>
-    <t>0.0123,0.0099,0.9754,0.0178</t>
-  </si>
-  <si>
-    <t>0.0342,0.0420,0.9443,0.0072</t>
-  </si>
-  <si>
-    <t>0.1489,0.0196,0.9109,0.0010</t>
-  </si>
-  <si>
-    <t>0.1576,0.0050,0.9090,0.0011</t>
-  </si>
-  <si>
-    <t>0.0145,0.1369,0.9422,0.0019</t>
-  </si>
-  <si>
-    <t>0.9971,0.0008,0.0002,0.0008</t>
-  </si>
-  <si>
-    <t>0.9978,0.0009,0.0003,0.0003</t>
-  </si>
-  <si>
-    <t>0.9932,0.0073,0.0006,0.0002</t>
-  </si>
-  <si>
-    <t>0.9947,0.0066,0.0004,0.0001</t>
-  </si>
-  <si>
-    <t>0.9945,0.0044,0.0009,0.0003</t>
-  </si>
-  <si>
-    <t>0.9970,0.0021,0.0003,0.0002</t>
-  </si>
-  <si>
-    <t>0.9968,0.0009,0.0003,0.0011</t>
-  </si>
-  <si>
-    <t>0.9990,0.0005,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.0054,0.1813,0.9728,0.0064</t>
-  </si>
-  <si>
-    <t>0.0968,0.1767,0.8498,0.0094</t>
-  </si>
-  <si>
-    <t>0.9925,0.0024,0.0017,0.0007</t>
-  </si>
-  <si>
-    <t>0.0027,0.0009,0.9966,0.0004</t>
-  </si>
-  <si>
-    <t>0.0014,0.0017,0.9939,0.0036</t>
-  </si>
-  <si>
-    <t>0.0098,0.0699,0.9651,0.0008</t>
-  </si>
-  <si>
-    <t>0.0042,0.0022,0.9977,0.0001</t>
-  </si>
-  <si>
-    <t>0.0052,0.0006,0.9958,0.0003</t>
-  </si>
-  <si>
-    <t>0.0002,0.0006,0.9996,0.0001</t>
-  </si>
-  <si>
-    <t>0.0126,0.0047,0.9878,0.0008</t>
-  </si>
-  <si>
-    <t>0.1076,0.0245,0.8875,0.0068</t>
-  </si>
-  <si>
-    <t>0.9337,0.0010,0.0776,0.0014</t>
-  </si>
-  <si>
-    <t>0.1910,0.0026,0.8153,0.0081</t>
-  </si>
-  <si>
-    <t>0.9932,0.0011,0.0014,0.0003</t>
-  </si>
-  <si>
-    <t>0.9977,0.0014,0.0001,0.0003</t>
-  </si>
-  <si>
-    <t>0.9936,0.0060,0.0008,0.0002</t>
-  </si>
-  <si>
-    <t>0.9949,0.0021,0.0019,0.0001</t>
-  </si>
-  <si>
-    <t>0.9914,0.0081,0.0012,0.0003</t>
-  </si>
-  <si>
-    <t>0.9967,0.0004,0.0012,0.0001</t>
-  </si>
-  <si>
-    <t>0.9974,0.0015,0.0002,0.0004</t>
-  </si>
-  <si>
-    <t>0.9946,0.0019,0.0001,0.0018</t>
-  </si>
-  <si>
-    <t>0.0105,0.7234,0.2632,0.0025</t>
-  </si>
-  <si>
-    <t>0.0064,0.0079,0.9935,0.0004</t>
-  </si>
-  <si>
-    <t>0.0188,0.1156,0.9517,0.0019</t>
-  </si>
-  <si>
-    <t>0.0046,0.0026,0.9949,0.0002</t>
-  </si>
-  <si>
-    <t>0.0007,0.0002,0.9989,0.0002</t>
-  </si>
-  <si>
-    <t>0.0159,0.0105,0.9603,0.0547</t>
-  </si>
-  <si>
-    <t>0.1802,0.0139,0.8575,0.0100</t>
-  </si>
-  <si>
-    <t>0.0885,0.0141,0.7592,0.1398</t>
-  </si>
-  <si>
-    <t>0.9872,0.0002,0.0008,0.0089</t>
-  </si>
-  <si>
-    <t>0.0088,0.2023,0.0022,0.9775</t>
-  </si>
-  <si>
-    <t>0.0621,0.0061,0.0061,0.9613</t>
-  </si>
-  <si>
-    <t>0.0005,0.0005,0.0013,0.9991</t>
-  </si>
-  <si>
-    <t>0.0042,0.0028,0.0003,0.9975</t>
-  </si>
-  <si>
-    <t>0.9877,0.0031,0.0007,0.0037</t>
+    <t>1,0,1,0</t>
+  </si>
+  <si>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
+    <t>0.9533,0.0147,0.0110,0.0086</t>
+  </si>
+  <si>
+    <t>0.0236,0.0004,0.0008,0.9910</t>
+  </si>
+  <si>
+    <t>0.8794,0.0024,0.0006,0.1408</t>
+  </si>
+  <si>
+    <t>0.0604,0.0037,0.0012,0.9821</t>
+  </si>
+  <si>
+    <t>0.9990,0.0004,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9964,0.0018,0.0005,0.0003</t>
+  </si>
+  <si>
+    <t>0.9980,0.0009,0.0002,0.0003</t>
+  </si>
+  <si>
+    <t>0.9988,0.0003,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.9939,0.0054,0.0003,0.0004</t>
+  </si>
+  <si>
+    <t>0.9976,0.0015,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9987,0.0003,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.9993,0.0003,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9013,0.0197,0.0802,0.0041</t>
+  </si>
+  <si>
+    <t>0.0796,0.0028,0.9588,0.0009</t>
+  </si>
+  <si>
+    <t>0.6665,0.0021,0.5530,0.0001</t>
+  </si>
+  <si>
+    <t>0.0208,0.0176,0.9611,0.0018</t>
+  </si>
+  <si>
+    <t>0.6290,0.0084,0.4689,0.0029</t>
+  </si>
+  <si>
+    <t>0.0053,0.9916,0.0045,0.0002</t>
+  </si>
+  <si>
+    <t>0.0015,0.9962,0.0017,0.0003</t>
+  </si>
+  <si>
+    <t>0.0175,0.9765,0.0187,0.0009</t>
+  </si>
+  <si>
+    <t>0.0133,0.9860,0.0021,0.0003</t>
+  </si>
+  <si>
+    <t>0.0021,0.9970,0.0005,0.0000</t>
+  </si>
+  <si>
+    <t>0.9242,0.0014,0.1168,0.0007</t>
+  </si>
+  <si>
+    <t>0.0060,0.0059,0.9868,0.0017</t>
+  </si>
+  <si>
+    <t>0.0043,0.0004,0.9959,0.0003</t>
+  </si>
+  <si>
+    <t>0.3328,0.0016,0.8391,0.0003</t>
+  </si>
+  <si>
+    <t>0.0355,0.0012,0.9851,0.0008</t>
+  </si>
+  <si>
+    <t>0.0398,0.0025,0.9660,0.0062</t>
+  </si>
+  <si>
+    <t>0.0053,0.0011,0.9962,0.0002</t>
+  </si>
+  <si>
+    <t>0.7193,0.3482,0.0132,0.0016</t>
+  </si>
+  <si>
+    <t>0.4620,0.4813,0.0895,0.0042</t>
+  </si>
+  <si>
+    <t>0.0019,0.0234,0.9967,0.0015</t>
+  </si>
+  <si>
+    <t>0.0119,0.9256,0.1904,0.0003</t>
+  </si>
+  <si>
+    <t>0.9737,0.0153,0.0072,0.0024</t>
+  </si>
+  <si>
+    <t>0.8963,0.0624,0.0354,0.0037</t>
+  </si>
+  <si>
+    <t>0.2066,0.8777,0.0013,0.0002</t>
+  </si>
+  <si>
+    <t>0.0062,0.9866,0.0773,0.0004</t>
+  </si>
+  <si>
+    <t>0.0437,0.5126,0.4424,0.0409</t>
+  </si>
+  <si>
+    <t>0.2681,0.0008,0.7461,0.0039</t>
+  </si>
+  <si>
+    <t>0.4588,0.0068,0.7000,0.0022</t>
+  </si>
+  <si>
+    <t>0.2149,0.0027,0.7990,0.0128</t>
+  </si>
+  <si>
+    <t>0.0098,0.0750,0.9859,0.0007</t>
+  </si>
+  <si>
+    <t>0.0053,0.9848,0.0053,0.0003</t>
+  </si>
+  <si>
+    <t>0.0004,0.0044,0.9963,0.0049</t>
+  </si>
+  <si>
+    <t>0.1326,0.4551,0.0580,0.7467</t>
+  </si>
+  <si>
+    <t>0.0035,0.9881,0.0146,0.0104</t>
+  </si>
+  <si>
+    <t>0.0128,0.9767,0.0077,0.0004</t>
+  </si>
+  <si>
+    <t>0.0053,0.9862,0.0536,0.0027</t>
+  </si>
+  <si>
+    <t>0.0018,0.0341,0.9949,0.0010</t>
+  </si>
+  <si>
+    <t>0.0030,0.1066,0.9863,0.0002</t>
+  </si>
+  <si>
+    <t>0.0517,0.0131,0.9392,0.0030</t>
+  </si>
+  <si>
+    <t>0.0034,0.0010,0.9967,0.0003</t>
+  </si>
+  <si>
+    <t>0.0102,0.0042,0.9917,0.0007</t>
+  </si>
+  <si>
+    <t>0.0091,0.2032,0.9213,0.0037</t>
+  </si>
+  <si>
+    <t>0.9853,0.0358,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.9959,0.0010,0.0005,0.0007</t>
+  </si>
+  <si>
+    <t>0.9825,0.0055,0.0100,0.0005</t>
+  </si>
+  <si>
+    <t>0.0202,0.2639,0.9353,0.0205</t>
+  </si>
+  <si>
+    <t>0.9934,0.0033,0.0018,0.0005</t>
+  </si>
+  <si>
+    <t>0.9974,0.0009,0.0006,0.0003</t>
+  </si>
+  <si>
+    <t>0.9920,0.0064,0.0010,0.0005</t>
+  </si>
+  <si>
+    <t>0.0011,0.9117,0.9897,0.0001</t>
+  </si>
+  <si>
+    <t>0.0061,0.0223,0.9872,0.0026</t>
+  </si>
+  <si>
+    <t>0.0006,0.0050,0.9982,0.0008</t>
+  </si>
+  <si>
+    <t>0.0007,0.9631,0.9501,0.0001</t>
+  </si>
+  <si>
+    <t>0.0003,0.0104,0.9977,0.0012</t>
+  </si>
+  <si>
+    <t>0.0724,0.9346,0.0069,0.0001</t>
+  </si>
+  <si>
+    <t>0.0062,0.9921,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.0161,0.0068,0.9859,0.0031</t>
+  </si>
+  <si>
+    <t>0.3187,0.0444,0.6832,0.0016</t>
+  </si>
+  <si>
+    <t>0.0078,0.0437,0.9875,0.0032</t>
+  </si>
+  <si>
+    <t>0.0019,0.9394,0.8478,0.0004</t>
+  </si>
+  <si>
+    <t>0.0005,0.8789,0.9871,0.0001</t>
+  </si>
+  <si>
+    <t>0.0008,0.9966,0.0336,0.0001</t>
+  </si>
+  <si>
+    <t>0.0013,0.9787,0.7295,0.0012</t>
+  </si>
+  <si>
+    <t>0.0058,0.0006,0.0020,0.9956</t>
+  </si>
+  <si>
+    <t>0.0013,0.0061,0.0008,0.9978</t>
+  </si>
+  <si>
+    <t>0.0114,0.0004,0.0009,0.9945</t>
+  </si>
+  <si>
+    <t>0.0127,0.0010,0.0003,0.9951</t>
+  </si>
+  <si>
+    <t>0.0449,0.0025,0.0006,0.9837</t>
+  </si>
+  <si>
+    <t>0.0033,0.0146,0.0004,0.9958</t>
+  </si>
+  <si>
+    <t>0.0008,0.9723,0.9616,0.0001</t>
+  </si>
+  <si>
+    <t>0.0014,0.8332,0.9902,0.0001</t>
+  </si>
+  <si>
+    <t>0.0284,0.5656,0.6901,0.0063</t>
+  </si>
+  <si>
+    <t>0.0011,0.8337,0.9531,0.0001</t>
+  </si>
+  <si>
+    <t>0.0011,0.9309,0.9692,0.0002</t>
+  </si>
+  <si>
+    <t>0.0006,0.9913,0.3010,0.0001</t>
+  </si>
+  <si>
+    <t>0.9986,0.0005,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9924,0.0072,0.0008,0.0003</t>
+  </si>
+  <si>
+    <t>0.9674,0.0343,0.0042,0.0008</t>
+  </si>
+  <si>
+    <t>0.9936,0.0054,0.0004,0.0005</t>
+  </si>
+  <si>
+    <t>0.9957,0.0021,0.0005,0.0004</t>
+  </si>
+  <si>
+    <t>0.9965,0.0016,0.0006,0.0005</t>
+  </si>
+  <si>
+    <t>0.9955,0.0012,0.0011,0.0004</t>
+  </si>
+  <si>
+    <t>0.9942,0.0050,0.0007,0.0003</t>
+  </si>
+  <si>
+    <t>0.9976,0.0009,0.0003,0.0004</t>
+  </si>
+  <si>
+    <t>0.9982,0.0003,0.0003,0.0003</t>
+  </si>
+  <si>
+    <t>0.9991,0.0003,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9991,0.0001,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9988,0.0004,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9991,0.0002,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9990,0.0001,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9973,0.0011,0.0003,0.0004</t>
+  </si>
+  <si>
+    <t>0.0052,0.0013,0.9956,0.0009</t>
+  </si>
+  <si>
+    <t>0.0816,0.0752,0.8721,0.0008</t>
+  </si>
+  <si>
+    <t>0.9433,0.0045,0.0219,0.0092</t>
+  </si>
+  <si>
+    <t>0.0157,0.0002,0.9941,0.0001</t>
+  </si>
+  <si>
+    <t>0.0075,0.9885,0.0013,0.0005</t>
+  </si>
+  <si>
+    <t>0.0034,0.9931,0.0066,0.0004</t>
+  </si>
+  <si>
+    <t>0.0022,0.9954,0.0016,0.0003</t>
+  </si>
+  <si>
+    <t>0.0061,0.9916,0.0007,0.0002</t>
+  </si>
+  <si>
+    <t>0.0064,0.9898,0.0028,0.0003</t>
+  </si>
+  <si>
+    <t>0.0023,0.9958,0.0005,0.0000</t>
+  </si>
+  <si>
+    <t>0.2661,0.8293,0.0018,0.0001</t>
+  </si>
+  <si>
+    <t>0.4426,0.4248,0.1550,0.0225</t>
+  </si>
+  <si>
+    <t>0.7415,0.0084,0.4020,0.0026</t>
+  </si>
+  <si>
+    <t>0.5633,0.0218,0.4831,0.0115</t>
+  </si>
+  <si>
+    <t>0.3375,0.0151,0.7552,0.0022</t>
+  </si>
+  <si>
+    <t>0.0356,0.0393,0.1435,0.9287</t>
+  </si>
+  <si>
+    <t>0.0074,0.9826,0.0127,0.0020</t>
+  </si>
+  <si>
+    <t>0.0264,0.9628,0.0464,0.0015</t>
+  </si>
+  <si>
+    <t>0.0018,0.9941,0.0173,0.0007</t>
+  </si>
+  <si>
+    <t>0.0036,0.9896,0.1290,0.0008</t>
+  </si>
+  <si>
+    <t>0.2139,0.8671,0.0012,0.0001</t>
+  </si>
+  <si>
+    <t>0.2254,0.7551,0.0769,0.0026</t>
+  </si>
+  <si>
+    <t>0.9468,0.0375,0.0141,0.0008</t>
+  </si>
+  <si>
+    <t>0.9970,0.0004,0.0010,0.0002</t>
+  </si>
+  <si>
+    <t>0.9937,0.0010,0.0017,0.0008</t>
+  </si>
+  <si>
+    <t>0.9979,0.0007,0.0002,0.0003</t>
+  </si>
+  <si>
+    <t>0.9984,0.0002,0.0003,0.0002</t>
+  </si>
+  <si>
+    <t>0.9991,0.0001,0.0001,0.0003</t>
+  </si>
+  <si>
+    <t>0.9959,0.0008,0.0015,0.0002</t>
+  </si>
+  <si>
+    <t>0.9968,0.0010,0.0004,0.0004</t>
+  </si>
+  <si>
+    <t>0.9983,0.0004,0.0003,0.0002</t>
+  </si>
+  <si>
+    <t>0.0014,0.7549,0.9778,0.0004</t>
+  </si>
+  <si>
+    <t>0.0007,0.5111,0.9919,0.0001</t>
+  </si>
+  <si>
+    <t>0.0014,0.0045,0.9972,0.0003</t>
+  </si>
+  <si>
+    <t>0.0016,0.0241,0.9907,0.0004</t>
+  </si>
+  <si>
+    <t>0.9952,0.0006,0.0010,0.0002</t>
+  </si>
+  <si>
+    <t>0.6698,0.0055,0.2982,0.0130</t>
+  </si>
+  <si>
+    <t>0.6629,0.0003,0.6131,0.0004</t>
+  </si>
+  <si>
+    <t>0.8014,0.0370,0.1867,0.0205</t>
+  </si>
+  <si>
+    <t>0.0480,0.0019,0.0006,0.9858</t>
+  </si>
+  <si>
+    <t>0.0001,0.0002,0.0003,0.9998</t>
+  </si>
+  <si>
+    <t>0.0094,0.0012,0.0002,0.9966</t>
+  </si>
+  <si>
+    <t>0.0157,0.0003,0.0002,0.9959</t>
+  </si>
+  <si>
+    <t>0.0015,0.6646,0.9851,0.0001</t>
+  </si>
+  <si>
+    <t>0.9960,0.0007,0.0007,0.0009</t>
+  </si>
+  <si>
+    <t>0.9383,0.0470,0.0043,0.0091</t>
+  </si>
+  <si>
+    <t>0.9984,0.0004,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.7276,0.3403,0.0053,0.0025</t>
+  </si>
+  <si>
+    <t>0.9970,0.0003,0.0007,0.0003</t>
+  </si>
+  <si>
+    <t>0.8592,0.0267,0.0110,0.1196</t>
+  </si>
+  <si>
+    <t>0.9969,0.0003,0.0011,0.0001</t>
+  </si>
+  <si>
+    <t>0.0015,0.2413,0.9730,0.0151</t>
+  </si>
+  <si>
+    <t>0.9477,0.0005,0.0044,0.0487</t>
+  </si>
+  <si>
+    <t>0.9212,0.0061,0.0194,0.0398</t>
+  </si>
+  <si>
+    <t>0.1734,0.8526,0.0115,0.0018</t>
+  </si>
+  <si>
+    <t>0.9930,0.0019,0.0012,0.0003</t>
+  </si>
+  <si>
+    <t>0.9680,0.0075,0.0158,0.0010</t>
+  </si>
+  <si>
+    <t>0.1692,0.8592,0.0036,0.0019</t>
+  </si>
+  <si>
+    <t>0.5817,0.1475,0.3269,0.0063</t>
+  </si>
+  <si>
+    <t>0.9821,0.0073,0.0050,0.0005</t>
+  </si>
+  <si>
+    <t>0.9882,0.0058,0.0010,0.0024</t>
+  </si>
+  <si>
+    <t>0.9963,0.0017,0.0004,0.0005</t>
+  </si>
+  <si>
+    <t>0.9985,0.0005,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9960,0.0009,0.0010,0.0003</t>
+  </si>
+  <si>
+    <t>0.9916,0.0017,0.0027,0.0009</t>
+  </si>
+  <si>
+    <t>0.9961,0.0022,0.0006,0.0002</t>
+  </si>
+  <si>
+    <t>0.9955,0.0011,0.0010,0.0008</t>
+  </si>
+  <si>
+    <t>0.9973,0.0014,0.0001,0.0003</t>
+  </si>
+  <si>
+    <t>0.9092,0.1617,0.0004,0.0003</t>
+  </si>
+  <si>
+    <t>0.7582,0.3352,0.0074,0.0004</t>
+  </si>
+  <si>
+    <t>0.9553,0.0447,0.0058,0.0004</t>
+  </si>
+  <si>
+    <t>0.3240,0.0428,0.7464,0.0086</t>
+  </si>
+  <si>
+    <t>0.9981,0.0020,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9894,0.0065,0.0016,0.0008</t>
+  </si>
+  <si>
+    <t>0.9906,0.0090,0.0014,0.0002</t>
+  </si>
+  <si>
+    <t>0.9838,0.0067,0.0041,0.0019</t>
+  </si>
+  <si>
+    <t>0.0010,0.0064,0.9988,0.0003</t>
+  </si>
+  <si>
+    <t>0.9898,0.0068,0.0019,0.0004</t>
+  </si>
+  <si>
+    <t>0.0070,0.0040,0.9907,0.0003</t>
+  </si>
+  <si>
+    <t>0.0013,0.0150,0.9954,0.0023</t>
+  </si>
+  <si>
+    <t>0.0021,0.0072,0.9927,0.0134</t>
+  </si>
+  <si>
+    <t>0.0073,0.0133,0.9911,0.0004</t>
+  </si>
+  <si>
+    <t>0.0013,0.0160,0.9919,0.0068</t>
+  </si>
+  <si>
+    <t>0.0245,0.0006,0.9861,0.0005</t>
+  </si>
+  <si>
+    <t>0.0037,0.0054,0.9925,0.0018</t>
+  </si>
+  <si>
+    <t>0.1698,0.0118,0.8483,0.0050</t>
+  </si>
+  <si>
+    <t>0.5245,0.0498,0.4244,0.0015</t>
+  </si>
+  <si>
+    <t>0.2150,0.0772,0.6975,0.0071</t>
+  </si>
+  <si>
+    <t>0.0608,0.2257,0.7669,0.0024</t>
+  </si>
+  <si>
+    <t>0.0248,0.8806,0.0929,0.0103</t>
+  </si>
+  <si>
+    <t>0.5429,0.0362,0.3699,0.0017</t>
+  </si>
+  <si>
+    <t>0.7673,0.0058,0.0688,0.0775</t>
+  </si>
+  <si>
+    <t>0.6464,0.0405,0.3872,0.0039</t>
+  </si>
+  <si>
+    <t>0.3912,0.7774,0.0013,0.0001</t>
+  </si>
+  <si>
+    <t>0.0305,0.9767,0.0008,0.0002</t>
+  </si>
+  <si>
+    <t>0.9015,0.1923,0.0005,0.0003</t>
+  </si>
+  <si>
+    <t>0.9009,0.1730,0.0025,0.0003</t>
+  </si>
+  <si>
+    <t>0.0729,0.9376,0.0011,0.0016</t>
+  </si>
+  <si>
+    <t>0.9637,0.0023,0.0319,0.0005</t>
+  </si>
+  <si>
+    <t>0.9928,0.0001,0.0050,0.0001</t>
+  </si>
+  <si>
+    <t>0.9910,0.0008,0.0019,0.0008</t>
+  </si>
+  <si>
+    <t>0.8292,0.0026,0.2813,0.0010</t>
+  </si>
+  <si>
+    <t>0.7730,0.0014,0.3016,0.0024</t>
+  </si>
+  <si>
+    <t>0.0389,0.0070,0.9568,0.0089</t>
+  </si>
+  <si>
+    <t>0.0224,0.5770,0.8071,0.0138</t>
+  </si>
+  <si>
+    <t>0.3849,0.0076,0.7152,0.0010</t>
+  </si>
+  <si>
+    <t>0.0184,0.0004,0.9887,0.0002</t>
+  </si>
+  <si>
+    <t>0.0045,0.0414,0.9523,0.0074</t>
+  </si>
+  <si>
+    <t>0.9958,0.0011,0.0006,0.0009</t>
+  </si>
+  <si>
+    <t>0.9916,0.0042,0.0015,0.0007</t>
+  </si>
+  <si>
+    <t>0.9933,0.0043,0.0005,0.0013</t>
+  </si>
+  <si>
+    <t>0.9937,0.0065,0.0006,0.0002</t>
+  </si>
+  <si>
+    <t>0.9906,0.0052,0.0022,0.0009</t>
+  </si>
+  <si>
+    <t>0.9956,0.0019,0.0014,0.0001</t>
+  </si>
+  <si>
+    <t>0.9975,0.0009,0.0002,0.0006</t>
+  </si>
+  <si>
+    <t>0.9984,0.0004,0.0001,0.0003</t>
+  </si>
+  <si>
+    <t>0.0379,0.0368,0.9513,0.0048</t>
+  </si>
+  <si>
+    <t>0.3564,0.2798,0.3738,0.0190</t>
+  </si>
+  <si>
+    <t>0.9904,0.0029,0.0016,0.0019</t>
+  </si>
+  <si>
+    <t>0.0055,0.0034,0.9929,0.0006</t>
+  </si>
+  <si>
+    <t>0.0023,0.0023,0.9941,0.0011</t>
+  </si>
+  <si>
+    <t>0.0564,0.0954,0.8920,0.0023</t>
+  </si>
+  <si>
+    <t>0.0019,0.0078,0.9960,0.0010</t>
+  </si>
+  <si>
+    <t>0.0017,0.0011,0.9971,0.0005</t>
+  </si>
+  <si>
+    <t>0.0002,0.0005,0.9996,0.0001</t>
+  </si>
+  <si>
+    <t>0.0074,0.0032,0.9908,0.0005</t>
+  </si>
+  <si>
+    <t>0.0125,0.0357,0.9680,0.0049</t>
+  </si>
+  <si>
+    <t>0.9703,0.0008,0.0217,0.0010</t>
+  </si>
+  <si>
+    <t>0.1973,0.0035,0.8702,0.0019</t>
+  </si>
+  <si>
+    <t>0.9736,0.0029,0.0112,0.0012</t>
+  </si>
+  <si>
+    <t>0.9728,0.0256,0.0068,0.0007</t>
+  </si>
+  <si>
+    <t>0.9979,0.0008,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9947,0.0005,0.0038,0.0001</t>
+  </si>
+  <si>
+    <t>0.9934,0.0068,0.0003,0.0003</t>
+  </si>
+  <si>
+    <t>0.9900,0.0058,0.0016,0.0027</t>
+  </si>
+  <si>
+    <t>0.9937,0.0019,0.0017,0.0005</t>
+  </si>
+  <si>
+    <t>0.9946,0.0070,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.9919,0.0093,0.0010,0.0003</t>
+  </si>
+  <si>
+    <t>0.0053,0.0478,0.9739,0.0005</t>
+  </si>
+  <si>
+    <t>0.0053,0.0087,0.9939,0.0002</t>
+  </si>
+  <si>
+    <t>0.0138,0.0518,0.9499,0.0213</t>
+  </si>
+  <si>
+    <t>0.0392,0.0290,0.9371,0.0113</t>
+  </si>
+  <si>
+    <t>0.0047,0.0013,0.9927,0.0017</t>
+  </si>
+  <si>
+    <t>0.0897,0.0197,0.8401,0.1394</t>
+  </si>
+  <si>
+    <t>0.1414,0.0247,0.8711,0.0060</t>
+  </si>
+  <si>
+    <t>0.2537,0.0100,0.7396,0.0212</t>
+  </si>
+  <si>
+    <t>0.9629,0.0032,0.0064,0.0167</t>
+  </si>
+  <si>
+    <t>0.1886,0.0459,0.0014,0.8572</t>
+  </si>
+  <si>
+    <t>0.1024,0.0092,0.0012,0.9544</t>
+  </si>
+  <si>
+    <t>0.0082,0.0001,0.0001,0.9974</t>
+  </si>
+  <si>
+    <t>0.0019,0.0013,0.0002,0.9987</t>
+  </si>
+  <si>
+    <t>0.9617,0.0061,0.0152,0.0056</t>
   </si>
 </sst>
 </file>
@@ -1953,7 +1962,7 @@
         <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1967,7 +1976,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1981,7 +1990,7 @@
         <v>259</v>
       </c>
       <c r="D4" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1995,7 +2004,7 @@
         <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2009,7 +2018,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2023,7 +2032,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2037,7 +2046,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2051,7 +2060,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2065,7 +2074,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2079,7 +2088,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2093,7 +2102,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2107,7 +2116,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2121,7 +2130,7 @@
         <v>259</v>
       </c>
       <c r="D14" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2132,10 +2141,10 @@
         <v>261</v>
       </c>
       <c r="C15" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D15" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2146,10 +2155,10 @@
         <v>261</v>
       </c>
       <c r="C16" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D16" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2163,7 +2172,7 @@
         <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2177,7 +2186,7 @@
         <v>259</v>
       </c>
       <c r="D18" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2191,7 +2200,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2205,7 +2214,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2219,7 +2228,7 @@
         <v>262</v>
       </c>
       <c r="D21" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2233,7 +2242,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2247,7 +2256,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2261,7 +2270,7 @@
         <v>259</v>
       </c>
       <c r="D24" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2275,7 +2284,7 @@
         <v>261</v>
       </c>
       <c r="D25" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2289,7 +2298,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2303,7 +2312,7 @@
         <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2317,7 +2326,7 @@
         <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2331,7 +2340,7 @@
         <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2345,7 +2354,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2359,7 +2368,7 @@
         <v>259</v>
       </c>
       <c r="D31" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2370,10 +2379,10 @@
         <v>259</v>
       </c>
       <c r="C32" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D32" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2387,7 +2396,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2401,7 +2410,7 @@
         <v>262</v>
       </c>
       <c r="D34" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2415,7 +2424,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2429,7 +2438,7 @@
         <v>259</v>
       </c>
       <c r="D36" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2440,10 +2449,10 @@
         <v>259</v>
       </c>
       <c r="C37" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D37" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2457,7 +2466,7 @@
         <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2471,7 +2480,7 @@
         <v>262</v>
       </c>
       <c r="D39" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2485,7 +2494,7 @@
         <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2499,7 +2508,7 @@
         <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2513,7 +2522,7 @@
         <v>261</v>
       </c>
       <c r="D42" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2527,7 +2536,7 @@
         <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2541,7 +2550,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2555,7 +2564,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2566,10 +2575,10 @@
         <v>259</v>
       </c>
       <c r="C46" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="D46" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2583,7 +2592,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2597,7 +2606,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2611,7 +2620,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2625,7 +2634,7 @@
         <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2639,7 +2648,7 @@
         <v>261</v>
       </c>
       <c r="D51" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2653,7 +2662,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2667,7 +2676,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2681,7 +2690,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2695,7 +2704,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2709,7 +2718,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2723,7 +2732,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2737,7 +2746,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2751,7 +2760,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2765,7 +2774,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2779,7 +2788,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2793,7 +2802,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2807,7 +2816,7 @@
         <v>263</v>
       </c>
       <c r="D63" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2821,7 +2830,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2835,7 +2844,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2849,7 +2858,7 @@
         <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2863,7 +2872,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2877,7 +2886,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2891,7 +2900,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2905,7 +2914,7 @@
         <v>261</v>
       </c>
       <c r="D70" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2916,10 +2925,10 @@
         <v>261</v>
       </c>
       <c r="C71" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D71" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2933,7 +2942,7 @@
         <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2947,7 +2956,7 @@
         <v>263</v>
       </c>
       <c r="D73" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2961,7 +2970,7 @@
         <v>263</v>
       </c>
       <c r="D74" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2975,7 +2984,7 @@
         <v>262</v>
       </c>
       <c r="D75" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2989,7 +2998,7 @@
         <v>263</v>
       </c>
       <c r="D76" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -3003,7 +3012,7 @@
         <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -3017,7 +3026,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -3031,7 +3040,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -3045,7 +3054,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -3059,7 +3068,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3073,7 +3082,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3087,7 +3096,7 @@
         <v>263</v>
       </c>
       <c r="D83" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3101,7 +3110,7 @@
         <v>263</v>
       </c>
       <c r="D84" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3112,10 +3121,10 @@
         <v>263</v>
       </c>
       <c r="C85" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D85" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3126,10 +3135,10 @@
         <v>263</v>
       </c>
       <c r="C86" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D86" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3140,10 +3149,10 @@
         <v>263</v>
       </c>
       <c r="C87" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D87" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3157,7 +3166,7 @@
         <v>262</v>
       </c>
       <c r="D88" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3171,7 +3180,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3185,7 +3194,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3199,7 +3208,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3213,7 +3222,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3227,7 +3236,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3241,7 +3250,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3255,7 +3264,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3269,7 +3278,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3283,7 +3292,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3297,7 +3306,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3311,7 +3320,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3325,7 +3334,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3339,7 +3348,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3353,7 +3362,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3367,7 +3376,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3381,7 +3390,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3395,7 +3404,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3409,7 +3418,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3423,7 +3432,7 @@
         <v>259</v>
       </c>
       <c r="D107" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3437,7 +3446,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3451,7 +3460,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3465,7 +3474,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3479,7 +3488,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3493,7 +3502,7 @@
         <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3507,7 +3516,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3521,7 +3530,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3532,10 +3541,10 @@
         <v>262</v>
       </c>
       <c r="C115" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D115" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3546,10 +3555,10 @@
         <v>259</v>
       </c>
       <c r="C116" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D116" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3560,10 +3569,10 @@
         <v>261</v>
       </c>
       <c r="C117" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D117" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3574,10 +3583,10 @@
         <v>259</v>
       </c>
       <c r="C118" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D118" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3591,7 +3600,7 @@
         <v>261</v>
       </c>
       <c r="D119" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3605,7 +3614,7 @@
         <v>260</v>
       </c>
       <c r="D120" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3619,7 +3628,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3633,7 +3642,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3647,7 +3656,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3661,7 +3670,7 @@
         <v>262</v>
       </c>
       <c r="D124" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3675,7 +3684,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3686,10 +3695,10 @@
         <v>259</v>
       </c>
       <c r="C126" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D126" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3703,7 +3712,7 @@
         <v>259</v>
       </c>
       <c r="D127" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3717,7 +3726,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3731,7 +3740,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3745,7 +3754,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3759,7 +3768,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3773,7 +3782,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3787,7 +3796,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3801,7 +3810,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3815,7 +3824,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3826,10 +3835,10 @@
         <v>263</v>
       </c>
       <c r="C136" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D136" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3840,10 +3849,10 @@
         <v>261</v>
       </c>
       <c r="C137" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D137" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3857,7 +3866,7 @@
         <v>261</v>
       </c>
       <c r="D138" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3871,7 +3880,7 @@
         <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3885,7 +3894,7 @@
         <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3899,7 +3908,7 @@
         <v>259</v>
       </c>
       <c r="D141" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3910,10 +3919,10 @@
         <v>261</v>
       </c>
       <c r="C142" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D142" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3927,7 +3936,7 @@
         <v>259</v>
       </c>
       <c r="D143" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3941,7 +3950,7 @@
         <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3955,7 +3964,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3969,7 +3978,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3983,7 +3992,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -3997,7 +4006,7 @@
         <v>263</v>
       </c>
       <c r="D148" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -4011,7 +4020,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -4022,10 +4031,10 @@
         <v>262</v>
       </c>
       <c r="C150" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D150" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -4039,7 +4048,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -4053,7 +4062,7 @@
         <v>259</v>
       </c>
       <c r="D152" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4067,7 +4076,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4081,7 +4090,7 @@
         <v>259</v>
       </c>
       <c r="D154" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4095,7 +4104,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4106,10 +4115,10 @@
         <v>261</v>
       </c>
       <c r="C156" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4123,7 +4132,7 @@
         <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4137,7 +4146,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4151,7 +4160,7 @@
         <v>262</v>
       </c>
       <c r="D159" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4165,7 +4174,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4179,7 +4188,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4190,10 +4199,10 @@
         <v>262</v>
       </c>
       <c r="C162" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D162" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4207,7 +4216,7 @@
         <v>259</v>
       </c>
       <c r="D163" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4221,7 +4230,7 @@
         <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4235,7 +4244,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4249,7 +4258,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4263,7 +4272,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4277,7 +4286,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4291,7 +4300,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4305,7 +4314,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4319,7 +4328,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4333,7 +4342,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4347,7 +4356,7 @@
         <v>259</v>
       </c>
       <c r="D173" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4361,7 +4370,7 @@
         <v>259</v>
       </c>
       <c r="D174" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4372,10 +4381,10 @@
         <v>262</v>
       </c>
       <c r="C175" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D175" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4389,7 +4398,7 @@
         <v>261</v>
       </c>
       <c r="D176" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4403,7 +4412,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4417,7 +4426,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4431,7 +4440,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4445,7 +4454,7 @@
         <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4459,7 +4468,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4473,7 +4482,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4487,7 +4496,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4501,7 +4510,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4515,7 +4524,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4529,7 +4538,7 @@
         <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4543,7 +4552,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4557,7 +4566,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4571,7 +4580,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4585,7 +4594,7 @@
         <v>261</v>
       </c>
       <c r="D190" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4596,10 +4605,10 @@
         <v>259</v>
       </c>
       <c r="C191" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D191" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4613,7 +4622,7 @@
         <v>261</v>
       </c>
       <c r="D192" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4624,10 +4633,10 @@
         <v>261</v>
       </c>
       <c r="C193" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D193" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4638,10 +4647,10 @@
         <v>261</v>
       </c>
       <c r="C194" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D194" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4655,7 +4664,7 @@
         <v>259</v>
       </c>
       <c r="D195" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4669,7 +4678,7 @@
         <v>259</v>
       </c>
       <c r="D196" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4680,10 +4689,10 @@
         <v>259</v>
       </c>
       <c r="C197" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D197" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4697,7 +4706,7 @@
         <v>262</v>
       </c>
       <c r="D198" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4711,7 +4720,7 @@
         <v>262</v>
       </c>
       <c r="D199" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4725,7 +4734,7 @@
         <v>259</v>
       </c>
       <c r="D200" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4739,7 +4748,7 @@
         <v>259</v>
       </c>
       <c r="D201" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4753,7 +4762,7 @@
         <v>262</v>
       </c>
       <c r="D202" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4767,7 +4776,7 @@
         <v>259</v>
       </c>
       <c r="D203" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4781,7 +4790,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4795,7 +4804,7 @@
         <v>259</v>
       </c>
       <c r="D205" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4809,7 +4818,7 @@
         <v>259</v>
       </c>
       <c r="D206" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4823,7 +4832,7 @@
         <v>259</v>
       </c>
       <c r="D207" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4837,7 +4846,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4848,10 +4857,10 @@
         <v>261</v>
       </c>
       <c r="C209" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D209" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4865,7 +4874,7 @@
         <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4879,7 +4888,7 @@
         <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4893,7 +4902,7 @@
         <v>261</v>
       </c>
       <c r="D212" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4907,7 +4916,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4921,7 +4930,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4935,7 +4944,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4949,7 +4958,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4963,7 +4972,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4977,7 +4986,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4991,7 +5000,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -5005,7 +5014,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -5019,7 +5028,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -5030,10 +5039,10 @@
         <v>259</v>
       </c>
       <c r="C222" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D222" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -5047,7 +5056,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5061,7 +5070,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5075,7 +5084,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5089,7 +5098,7 @@
         <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5103,7 +5112,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5117,7 +5126,7 @@
         <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5131,7 +5140,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5145,7 +5154,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5159,7 +5168,7 @@
         <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5173,7 +5182,7 @@
         <v>259</v>
       </c>
       <c r="D232" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5187,7 +5196,7 @@
         <v>261</v>
       </c>
       <c r="D233" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5201,7 +5210,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5215,7 +5224,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5229,7 +5238,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5243,7 +5252,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5257,7 +5266,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5271,7 +5280,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>323</v>
+        <v>503</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5285,7 +5294,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5299,7 +5308,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>502</v>
+        <v>505</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5313,7 +5322,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>503</v>
+        <v>506</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5324,10 +5333,10 @@
         <v>261</v>
       </c>
       <c r="C243" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5341,7 +5350,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>505</v>
+        <v>508</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5355,7 +5364,7 @@
         <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>506</v>
+        <v>509</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5369,7 +5378,7 @@
         <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5383,7 +5392,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5397,7 +5406,7 @@
         <v>261</v>
       </c>
       <c r="D248" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5411,7 +5420,7 @@
         <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5425,7 +5434,7 @@
         <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>511</v>
+        <v>514</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5439,7 +5448,7 @@
         <v>259</v>
       </c>
       <c r="D251" t="s">
-        <v>512</v>
+        <v>515</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5453,7 +5462,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5467,7 +5476,7 @@
         <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>514</v>
+        <v>517</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5481,7 +5490,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>515</v>
+        <v>518</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5495,7 +5504,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5509,7 +5518,7 @@
         <v>259</v>
       </c>
       <c r="D256" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
     </row>
   </sheetData>
